--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/8431-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/8431-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54243AF9-D9CF-4711-B0A3-40582CDB07BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60F5EA03-25D1-4E32-91E2-83FEF8660037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FC251C51-6B2D-4364-8172-52BED1DC7B15}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{D171C929-3007-42A5-9D0B-809C0F0EE9F8}"/>
   </bookViews>
   <sheets>
     <sheet name="8431-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1502,23 +1502,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8348DB9-7759-4E7E-B03C-A5629DC52105}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E93B73-CC80-4A37-A802-085F8D79CCDC}">
   <dimension ref="A1:R33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.77734375" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="7.77734375" customWidth="1"/>
-    <col min="5" max="5" width="7.44140625" customWidth="1"/>
-    <col min="6" max="7" width="7.77734375" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" customWidth="1"/>
-    <col min="9" max="10" width="7.77734375" customWidth="1"/>
-    <col min="11" max="17" width="7.44140625" customWidth="1"/>
-    <col min="18" max="18" width="8" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
+    <col min="5" max="5" width="9.375" customWidth="1"/>
+    <col min="6" max="7" width="9.75" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
+    <col min="9" max="10" width="9.75" customWidth="1"/>
+    <col min="11" max="17" width="9.375" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1672,7 +1672,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="41">
         <v>2025</v>
       </c>
@@ -1836,7 +1836,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="43" t="s">
         <v>26</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="22" t="s">
         <v>29</v>
@@ -1970,7 +1970,7 @@
       <c r="Q10" s="48"/>
       <c r="R10" s="48"/>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>26</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>2024</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="41">
         <v>2023</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2022</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>3.67</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>3.27</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="41">
         <v>2021</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2020</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="41">
         <v>2019</v>
       </c>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2018</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="41">
         <v>2017</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2016</v>
       </c>
@@ -2904,7 +2904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="41">
         <v>2015</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2014</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="41">
         <v>2013</v>
       </c>
@@ -3066,7 +3066,7 @@
         <v>5.07</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2012</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="41">
         <v>2011</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39" t="s">
         <v>40</v>
       </c>
